--- a/data/raw/sales/Week 10/Nexlev/other_channels.xlsx
+++ b/data/raw/sales/Week 10/Nexlev/other_channels.xlsx
@@ -555,7 +555,7 @@
       </c>
       <c r="C2" s="13" t="inlineStr">
         <is>
-          <t>ET-01 Black</t>
+          <t>ET-01-BK</t>
         </is>
       </c>
       <c r="D2" s="13" t="n">
@@ -667,7 +667,7 @@
       </c>
       <c r="C6" s="13" t="inlineStr">
         <is>
-          <t>ETC-05</t>
+          <t>ETC-05-PI</t>
         </is>
       </c>
       <c r="D6" s="13" t="n">
@@ -2496,7 +2496,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" s="16" t="inlineStr">
         <is>
-          <t>FBA79350</t>
+          <t>FBP79350</t>
         </is>
       </c>
       <c r="B12" s="13" t="inlineStr">
@@ -3010,7 +3010,7 @@
       </c>
       <c r="C30" s="16" t="inlineStr">
         <is>
-          <t>ETC-07</t>
+          <t>ETC-07-WH</t>
         </is>
       </c>
       <c r="D30" s="17" t="n">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="C33" s="16" t="inlineStr">
         <is>
-          <t>ETC-08</t>
+          <t>ETC-08-BL</t>
         </is>
       </c>
       <c r="D33" s="17" t="n">
@@ -3178,7 +3178,7 @@
       </c>
       <c r="C36" s="17" t="inlineStr">
         <is>
-          <t>V-01-RG</t>
+          <t>V-01 RG</t>
         </is>
       </c>
       <c r="D36" s="17" t="n">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="C37" s="17" t="inlineStr">
         <is>
-          <t>NP-07-WD</t>
+          <t>NP-07</t>
         </is>
       </c>
       <c r="D37" s="17" t="n">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="C38" s="17" t="inlineStr">
         <is>
-          <t>V-02-FS</t>
+          <t>V-02</t>
         </is>
       </c>
       <c r="D38" s="17" t="n">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="C6" s="16" t="inlineStr">
         <is>
-          <t>Blue CM-01</t>
+          <t>CM-01-BL</t>
         </is>
       </c>
       <c r="D6" s="16" t="n">
@@ -3448,7 +3448,7 @@
     <row r="7" ht="14.25" customHeight="1">
       <c r="A7" s="16" t="inlineStr">
         <is>
-          <t>FBA79598</t>
+          <t>FBK79598</t>
         </is>
       </c>
       <c r="B7" s="16" t="inlineStr">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="D8" s="19" t="inlineStr">
         <is>
-          <t>V-01 Rose Gold</t>
+          <t>V-01 RG</t>
         </is>
       </c>
       <c r="E8" s="14" t="n">
@@ -5270,7 +5270,7 @@
       </c>
       <c r="B21" s="19" t="inlineStr">
         <is>
-          <t>FBA79350</t>
+          <t>FBP79350</t>
         </is>
       </c>
       <c r="C21" s="19" t="inlineStr">
@@ -6204,7 +6204,7 @@
       </c>
       <c r="D54" s="19" t="inlineStr">
         <is>
-          <t>HD-02</t>
+          <t>HD-01</t>
         </is>
       </c>
       <c r="E54" s="14" t="n">
@@ -6450,7 +6450,7 @@
       </c>
       <c r="C2" s="22" t="inlineStr">
         <is>
-          <t>ET-01 BK</t>
+          <t>ET-01-BK</t>
         </is>
       </c>
       <c r="D2" s="21" t="n">
@@ -6478,7 +6478,7 @@
       </c>
       <c r="C3" s="22" t="inlineStr">
         <is>
-          <t>ET-02 GN</t>
+          <t>ET-02-GN</t>
         </is>
       </c>
       <c r="D3" s="21" t="n">
@@ -6496,7 +6496,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="21" t="inlineStr">
         <is>
-          <t>FBA79347</t>
+          <t>FBK79347</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -6506,7 +6506,7 @@
       </c>
       <c r="C4" s="22" t="inlineStr">
         <is>
-          <t>ETC-05</t>
+          <t>ETC-05-PI</t>
         </is>
       </c>
       <c r="D4" s="21" t="n">
@@ -6534,7 +6534,7 @@
       </c>
       <c r="C5" s="22" t="inlineStr">
         <is>
-          <t>ETC-08</t>
+          <t>ETC-08-BL</t>
         </is>
       </c>
       <c r="D5" s="21" t="n">
@@ -6675,7 +6675,7 @@
       </c>
       <c r="C3" s="21" t="inlineStr">
         <is>
-          <t>ET-02</t>
+          <t>ET-02-GN</t>
         </is>
       </c>
       <c r="D3" s="21" t="n">
@@ -6708,7 +6708,7 @@
       </c>
       <c r="C4" s="21" t="inlineStr">
         <is>
-          <t>VC 02</t>
+          <t>VC-02</t>
         </is>
       </c>
       <c r="D4" s="21" t="n">
@@ -6741,7 +6741,7 @@
       </c>
       <c r="C5" s="21" t="inlineStr">
         <is>
-          <t>VC 04</t>
+          <t>VC-04</t>
         </is>
       </c>
       <c r="D5" s="21" t="n">
@@ -6906,7 +6906,7 @@
       </c>
       <c r="C10" s="21" t="inlineStr">
         <is>
-          <t>CM-02</t>
+          <t>CM-02-PR</t>
         </is>
       </c>
       <c r="D10" s="21" t="n">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C31" s="21" t="inlineStr">
         <is>
-          <t>ETC-08</t>
+          <t>ETC-08-BL</t>
         </is>
       </c>
       <c r="D31" s="21" t="n">
